--- a/artfynd/A 55352-2023 artfynd.xlsx
+++ b/artfynd/A 55352-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 55352-2023 artfynd.xlsx
+++ b/artfynd/A 55352-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74464736</v>
       </c>
       <c r="B2" t="n">
-        <v>101691</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104060</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593890.2467593165</v>
+        <v>593890</v>
       </c>
       <c r="R2" t="n">
-        <v>6449140.111677494</v>
+        <v>6449140</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1982-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1983-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -804,12 +789,7 @@
         <v>74477658</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100773</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593890.2467593165</v>
+        <v>593890</v>
       </c>
       <c r="R3" t="n">
-        <v>6449140.111677494</v>
+        <v>6449140</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -874,19 +854,9 @@
           <t>1982-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1983-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -930,12 +900,7 @@
         <v>74551279</v>
       </c>
       <c r="B4" t="n">
-        <v>99382</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101662</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -967,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593890.2467593165</v>
+        <v>593890</v>
       </c>
       <c r="R4" t="n">
-        <v>6449140.111677494</v>
+        <v>6449140</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1000,19 +965,9 @@
           <t>1982-01-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1983-12-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1056,12 +1011,7 @@
         <v>74843231</v>
       </c>
       <c r="B5" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105554</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593890.2467593165</v>
+        <v>593890</v>
       </c>
       <c r="R5" t="n">
-        <v>6449140.111677494</v>
+        <v>6449140</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1126,19 +1076,9 @@
           <t>1982-01-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>1983-12-31</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1182,12 +1122,7 @@
         <v>74969244</v>
       </c>
       <c r="B6" t="n">
-        <v>106964</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109435</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593890.2467593165</v>
+        <v>593890</v>
       </c>
       <c r="R6" t="n">
-        <v>6449140.111677494</v>
+        <v>6449140</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1252,19 +1187,9 @@
           <t>1982-01-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>1983-12-31</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1308,12 +1233,7 @@
         <v>74977027</v>
       </c>
       <c r="B7" t="n">
-        <v>108203</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110713</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593890.2467593165</v>
+        <v>593890</v>
       </c>
       <c r="R7" t="n">
-        <v>6449140.111677494</v>
+        <v>6449140</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1378,19 +1298,9 @@
           <t>1982-01-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>1983-12-31</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">

--- a/artfynd/A 55352-2023 artfynd.xlsx
+++ b/artfynd/A 55352-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74464736</v>
       </c>
       <c r="B2" t="n">
-        <v>104060</v>
+        <v>104069</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74477658</v>
       </c>
       <c r="B3" t="n">
-        <v>100773</v>
+        <v>100779</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74551279</v>
       </c>
       <c r="B4" t="n">
-        <v>101662</v>
+        <v>101668</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74843231</v>
       </c>
       <c r="B5" t="n">
-        <v>105554</v>
+        <v>105563</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>74969244</v>
       </c>
       <c r="B6" t="n">
-        <v>109435</v>
+        <v>109444</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>74977027</v>
       </c>
       <c r="B7" t="n">
-        <v>110713</v>
+        <v>110722</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 55352-2023 artfynd.xlsx
+++ b/artfynd/A 55352-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74464736</v>
       </c>
       <c r="B2" t="n">
-        <v>104069</v>
+        <v>104072</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74477658</v>
       </c>
       <c r="B3" t="n">
-        <v>100779</v>
+        <v>100780</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74551279</v>
       </c>
       <c r="B4" t="n">
-        <v>101668</v>
+        <v>101669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74843231</v>
       </c>
       <c r="B5" t="n">
-        <v>105563</v>
+        <v>105566</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>74969244</v>
       </c>
       <c r="B6" t="n">
-        <v>109444</v>
+        <v>109449</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>74977027</v>
       </c>
       <c r="B7" t="n">
-        <v>110722</v>
+        <v>110727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 55352-2023 artfynd.xlsx
+++ b/artfynd/A 55352-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74464736</v>
       </c>
       <c r="B2" t="n">
-        <v>104072</v>
+        <v>104099</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74477658</v>
       </c>
       <c r="B3" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74551279</v>
       </c>
       <c r="B4" t="n">
-        <v>101669</v>
+        <v>101696</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74843231</v>
       </c>
       <c r="B5" t="n">
-        <v>105566</v>
+        <v>105594</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>74969244</v>
       </c>
       <c r="B6" t="n">
-        <v>109449</v>
+        <v>109477</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>74977027</v>
       </c>
       <c r="B7" t="n">
-        <v>110727</v>
+        <v>110755</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 55352-2023 artfynd.xlsx
+++ b/artfynd/A 55352-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74464736</v>
       </c>
       <c r="B2" t="n">
-        <v>104099</v>
+        <v>104105</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74477658</v>
       </c>
       <c r="B3" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74551279</v>
       </c>
       <c r="B4" t="n">
-        <v>101696</v>
+        <v>101702</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74843231</v>
       </c>
       <c r="B5" t="n">
-        <v>105594</v>
+        <v>105600</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>74969244</v>
       </c>
       <c r="B6" t="n">
-        <v>109477</v>
+        <v>109483</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>74977027</v>
       </c>
       <c r="B7" t="n">
-        <v>110755</v>
+        <v>110761</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 55352-2023 artfynd.xlsx
+++ b/artfynd/A 55352-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74464736</v>
       </c>
       <c r="B2" t="n">
-        <v>104105</v>
+        <v>104112</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74477658</v>
       </c>
       <c r="B3" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74551279</v>
       </c>
       <c r="B4" t="n">
-        <v>101702</v>
+        <v>101709</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74843231</v>
       </c>
       <c r="B5" t="n">
-        <v>105600</v>
+        <v>105607</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>74969244</v>
       </c>
       <c r="B6" t="n">
-        <v>109483</v>
+        <v>109490</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>74977027</v>
       </c>
       <c r="B7" t="n">
-        <v>110761</v>
+        <v>110768</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 55352-2023 artfynd.xlsx
+++ b/artfynd/A 55352-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74464736</v>
       </c>
       <c r="B2" t="n">
-        <v>104112</v>
+        <v>104116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74477658</v>
       </c>
       <c r="B3" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74551279</v>
       </c>
       <c r="B4" t="n">
-        <v>101709</v>
+        <v>101713</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74843231</v>
       </c>
       <c r="B5" t="n">
-        <v>105607</v>
+        <v>105611</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>74969244</v>
       </c>
       <c r="B6" t="n">
-        <v>109490</v>
+        <v>109494</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>74977027</v>
       </c>
       <c r="B7" t="n">
-        <v>110768</v>
+        <v>110772</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 55352-2023 artfynd.xlsx
+++ b/artfynd/A 55352-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74464736</v>
       </c>
       <c r="B2" t="n">
-        <v>104116</v>
+        <v>104123</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74477658</v>
       </c>
       <c r="B3" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74551279</v>
       </c>
       <c r="B4" t="n">
-        <v>101713</v>
+        <v>101720</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74843231</v>
       </c>
       <c r="B5" t="n">
-        <v>105611</v>
+        <v>105618</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>74969244</v>
       </c>
       <c r="B6" t="n">
-        <v>109494</v>
+        <v>109502</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>74977027</v>
       </c>
       <c r="B7" t="n">
-        <v>110772</v>
+        <v>110780</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 55352-2023 artfynd.xlsx
+++ b/artfynd/A 55352-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74464736</v>
       </c>
       <c r="B2" t="n">
-        <v>104126</v>
+        <v>104131</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74477658</v>
       </c>
       <c r="B3" t="n">
-        <v>100834</v>
+        <v>100839</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74551279</v>
       </c>
       <c r="B4" t="n">
-        <v>101723</v>
+        <v>101728</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74843231</v>
       </c>
       <c r="B5" t="n">
-        <v>105621</v>
+        <v>105626</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>74969244</v>
       </c>
       <c r="B6" t="n">
-        <v>109505</v>
+        <v>109510</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>74977027</v>
       </c>
       <c r="B7" t="n">
-        <v>110783</v>
+        <v>110788</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 55352-2023 artfynd.xlsx
+++ b/artfynd/A 55352-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74464736</v>
       </c>
       <c r="B2" t="n">
-        <v>104131</v>
+        <v>104139</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74477658</v>
       </c>
       <c r="B3" t="n">
-        <v>100839</v>
+        <v>100847</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74551279</v>
       </c>
       <c r="B4" t="n">
-        <v>101728</v>
+        <v>101736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74843231</v>
       </c>
       <c r="B5" t="n">
-        <v>105626</v>
+        <v>105634</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>74969244</v>
       </c>
       <c r="B6" t="n">
-        <v>109510</v>
+        <v>109518</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>74977027</v>
       </c>
       <c r="B7" t="n">
-        <v>110788</v>
+        <v>110796</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 55352-2023 artfynd.xlsx
+++ b/artfynd/A 55352-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74464736</v>
       </c>
       <c r="B2" t="n">
-        <v>104139</v>
+        <v>104149</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74477658</v>
       </c>
       <c r="B3" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74551279</v>
       </c>
       <c r="B4" t="n">
-        <v>101736</v>
+        <v>101746</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74843231</v>
       </c>
       <c r="B5" t="n">
-        <v>105634</v>
+        <v>105644</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>74969244</v>
       </c>
       <c r="B6" t="n">
-        <v>109518</v>
+        <v>109528</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>74977027</v>
       </c>
       <c r="B7" t="n">
-        <v>110796</v>
+        <v>110806</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
